--- a/docs/templates/customer-data-template.xlsx
+++ b/docs/templates/customer-data-template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CA4"/>
+  <dimension ref="A1:BV4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,210 +431,195 @@
         <v>salesmen.salesman_name</v>
       </c>
       <c r="K1" t="str">
-        <v>salesmen.employee_code</v>
+        <v>salesmen.phone_number</v>
       </c>
       <c r="L1" t="str">
-        <v>salesmen.external_salesman_id</v>
+        <v>salesmen.zone</v>
       </c>
       <c r="M1" t="str">
-        <v>salesmen.phone_number</v>
+        <v>salesmen.region</v>
       </c>
       <c r="N1" t="str">
-        <v>salesmen.zone</v>
+        <v>salesmen.area</v>
       </c>
       <c r="O1" t="str">
-        <v>salesmen.region</v>
+        <v>outlets.external_outlet_code</v>
       </c>
       <c r="P1" t="str">
-        <v>salesmen.area</v>
+        <v>outlets.outlet_name</v>
       </c>
       <c r="Q1" t="str">
-        <v>outlets.external_outlet_code</v>
+        <v>outlets.mobile_number</v>
       </c>
       <c r="R1" t="str">
-        <v>outlets.outlet_name</v>
+        <v>outlets.gst_number</v>
       </c>
       <c r="S1" t="str">
-        <v>outlets.mobile_number</v>
+        <v>outlets.address_line1</v>
       </c>
       <c r="T1" t="str">
-        <v>outlets.gst_number</v>
+        <v>outlets.address_line2</v>
       </c>
       <c r="U1" t="str">
-        <v>outlets.address_line1</v>
+        <v>outlets.pincode</v>
       </c>
       <c r="V1" t="str">
-        <v>outlets.address_line2</v>
+        <v>outlets.latitude</v>
       </c>
       <c r="W1" t="str">
-        <v>outlets.pincode</v>
+        <v>outlets.longitude</v>
       </c>
       <c r="X1" t="str">
-        <v>outlets.latitude</v>
+        <v>outlets.zone</v>
       </c>
       <c r="Y1" t="str">
-        <v>outlets.longitude</v>
+        <v>outlets.region</v>
       </c>
       <c r="Z1" t="str">
-        <v>outlets.zone</v>
+        <v>outlets.area</v>
       </c>
       <c r="AA1" t="str">
-        <v>outlets.region</v>
+        <v>brands.brand_name</v>
       </c>
       <c r="AB1" t="str">
-        <v>outlets.area</v>
+        <v>skus.sku_code</v>
       </c>
       <c r="AC1" t="str">
-        <v>tenant_outlets.tenant_outlet_code</v>
+        <v>skus.name</v>
       </c>
       <c r="AD1" t="str">
-        <v>brands.brand_code</v>
+        <v>skus.hsn_code</v>
       </c>
       <c r="AE1" t="str">
-        <v>brands.brand_name</v>
+        <v>skus.mrp</v>
       </c>
       <c r="AF1" t="str">
-        <v>skus.sku_code</v>
+        <v>skus.discount_amount</v>
       </c>
       <c r="AG1" t="str">
-        <v>skus.name</v>
+        <v>skus.discount_percent</v>
       </c>
       <c r="AH1" t="str">
-        <v>skus.hsn_code</v>
+        <v>skus.weight</v>
       </c>
       <c r="AI1" t="str">
-        <v>skus.mrp</v>
+        <v>skus.length_cm</v>
       </c>
       <c r="AJ1" t="str">
-        <v>skus.discount_amount</v>
+        <v>skus.width_cm</v>
       </c>
       <c r="AK1" t="str">
-        <v>skus.discount_percent</v>
+        <v>skus.height_cm</v>
       </c>
       <c r="AL1" t="str">
-        <v>skus.weight</v>
+        <v>skus.rate</v>
       </c>
       <c r="AM1" t="str">
-        <v>skus.length_cm</v>
+        <v>skus.sgst_percent</v>
       </c>
       <c r="AN1" t="str">
-        <v>skus.width_cm</v>
+        <v>skus.sgst_amount</v>
       </c>
       <c r="AO1" t="str">
-        <v>skus.height_cm</v>
+        <v>skus.cgst_percent</v>
       </c>
       <c r="AP1" t="str">
-        <v>skus.rate</v>
+        <v>skus.cgst_amount</v>
       </c>
       <c r="AQ1" t="str">
-        <v>skus.sgst_percent</v>
+        <v>skus.amount</v>
       </c>
       <c r="AR1" t="str">
-        <v>skus.sgst_amount</v>
+        <v>skus.igst_percent</v>
       </c>
       <c r="AS1" t="str">
-        <v>skus.cgst_percent</v>
+        <v>skus.igst_amount</v>
       </c>
       <c r="AT1" t="str">
-        <v>skus.cgst_amount</v>
+        <v>sales_orders.external_order_id</v>
       </c>
       <c r="AU1" t="str">
-        <v>skus.amount</v>
+        <v>sales_orders.external_invoice_no</v>
       </c>
       <c r="AV1" t="str">
-        <v>skus.igst_percent</v>
+        <v>sales_orders.external_awb_no</v>
       </c>
       <c r="AW1" t="str">
-        <v>skus.igst_amount</v>
+        <v>sales_orders.order_punched_at</v>
       </c>
       <c r="AX1" t="str">
-        <v>sales_orders.external_order_id</v>
+        <v>sales_orders.order_sale_date</v>
       </c>
       <c r="AY1" t="str">
-        <v>sales_orders.external_invoice_no</v>
+        <v>sales_orders.gross_amount</v>
       </c>
       <c r="AZ1" t="str">
-        <v>sales_orders.external_awb_no</v>
+        <v>sales_orders.discount_amount</v>
       </c>
       <c r="BA1" t="str">
-        <v>sales_orders.order_punched_at</v>
+        <v>sales_orders.tax_amount</v>
       </c>
       <c r="BB1" t="str">
-        <v>sales_orders.order_sale_date</v>
+        <v>sales_orders.net_amount</v>
       </c>
       <c r="BC1" t="str">
-        <v>sales_orders.gross_amount</v>
+        <v>sales_orders.collections_amount</v>
       </c>
       <c r="BD1" t="str">
-        <v>sales_orders.discount_amount</v>
+        <v>sales_orders.outstanding_amount</v>
       </c>
       <c r="BE1" t="str">
-        <v>sales_orders.tax_amount</v>
+        <v>sales_orders.decided_margin_amount</v>
       </c>
       <c r="BF1" t="str">
-        <v>sales_orders.net_amount</v>
+        <v>sales_orders.remarks</v>
       </c>
       <c r="BG1" t="str">
-        <v>sales_orders.collections_amount</v>
+        <v>sales_order_items.ordered_quantity</v>
       </c>
       <c r="BH1" t="str">
-        <v>sales_orders.outstanding_amount</v>
+        <v>sales_order_items.rate</v>
       </c>
       <c r="BI1" t="str">
-        <v>sales_orders.decided_margin_amount</v>
+        <v>sales_order_items.discount_amount</v>
       </c>
       <c r="BJ1" t="str">
-        <v>sales_orders.remarks</v>
+        <v>sales_order_items.discount_percent</v>
       </c>
       <c r="BK1" t="str">
-        <v>sales_order_items.external_line_id</v>
+        <v>sales_order_items.sgst_percent</v>
       </c>
       <c r="BL1" t="str">
-        <v>sales_order_items.ordered_quantity</v>
+        <v>sales_order_items.sgst_amount</v>
       </c>
       <c r="BM1" t="str">
-        <v>sales_order_items.rate</v>
+        <v>sales_order_items.cgst_percent</v>
       </c>
       <c r="BN1" t="str">
-        <v>sales_order_items.discount_amount</v>
+        <v>sales_order_items.cgst_amount</v>
       </c>
       <c r="BO1" t="str">
-        <v>sales_order_items.discount_percent</v>
+        <v>sales_order_items.igst_percent</v>
       </c>
       <c r="BP1" t="str">
-        <v>sales_order_items.sgst_percent</v>
+        <v>sales_order_items.igst_amount</v>
       </c>
       <c r="BQ1" t="str">
-        <v>sales_order_items.sgst_amount</v>
+        <v>sales_order_items.tax_amount</v>
       </c>
       <c r="BR1" t="str">
-        <v>sales_order_items.cgst_percent</v>
+        <v>sales_order_items.amount</v>
       </c>
       <c r="BS1" t="str">
-        <v>sales_order_items.cgst_amount</v>
+        <v>order_payments.payment_date</v>
       </c>
       <c r="BT1" t="str">
-        <v>sales_order_items.igst_percent</v>
+        <v>order_payments.payment_mode</v>
       </c>
       <c r="BU1" t="str">
-        <v>sales_order_items.igst_amount</v>
+        <v>order_payments.amount</v>
       </c>
       <c r="BV1" t="str">
-        <v>sales_order_items.tax_amount</v>
-      </c>
-      <c r="BW1" t="str">
-        <v>sales_order_items.amount</v>
-      </c>
-      <c r="BX1" t="str">
-        <v>order_payments.payment_date</v>
-      </c>
-      <c r="BY1" t="str">
-        <v>order_payments.payment_mode</v>
-      </c>
-      <c r="BZ1" t="str">
-        <v>order_payments.amount</v>
-      </c>
-      <c r="CA1" t="str">
         <v>order_payments.external_ref</v>
       </c>
     </row>
@@ -670,210 +655,195 @@
         <v>Ravi Kumar</v>
       </c>
       <c r="K2" t="str">
-        <v>EMP_1001</v>
+        <v>9876543210</v>
       </c>
       <c r="L2" t="str">
-        <v>EXT_SM_9001</v>
+        <v>SOUTH</v>
       </c>
       <c r="M2" t="str">
-        <v>9876543210</v>
+        <v>KARNATAKA</v>
       </c>
       <c r="N2" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="O2" t="str">
+        <v>OUT_0001</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Annapurna Stores</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="R2" t="str">
+        <v>29ABCDE1234F1Z5</v>
+      </c>
+      <c r="S2" t="str">
+        <v>12, 100 Feet Rd</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="U2" t="str">
+        <v>560038</v>
+      </c>
+      <c r="V2">
+        <v>12.9715987</v>
+      </c>
+      <c r="W2">
+        <v>77.6400001</v>
+      </c>
+      <c r="X2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Y2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Z2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="Q2" t="str">
-        <v>OUT_0001</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Annapurna Stores</v>
-      </c>
-      <c r="S2" t="str">
-        <v>9988776655</v>
-      </c>
-      <c r="T2" t="str">
-        <v>29ABCDE1234F1Z5</v>
-      </c>
-      <c r="U2" t="str">
-        <v>12, 100 Feet Rd</v>
-      </c>
-      <c r="V2" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="W2" t="str">
-        <v>560038</v>
-      </c>
-      <c r="X2">
-        <v>12.9715987</v>
-      </c>
-      <c r="Y2">
-        <v>77.6400001</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>SOUTH</v>
-      </c>
       <c r="AA2" t="str">
-        <v>KARNATAKA</v>
+        <v>Super Cola</v>
       </c>
       <c r="AB2" t="str">
-        <v>BENGALURU</v>
+        <v>SKU_COLA_250</v>
       </c>
       <c r="AC2" t="str">
-        <v>TOUT_0001</v>
+        <v>Super Cola 250ml</v>
       </c>
       <c r="AD2" t="str">
-        <v>BRAND_COLA</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>Super Cola</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>SKU_COLA_250</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>Super Cola 250ml</v>
-      </c>
-      <c r="AH2" t="str">
         <v>22021020</v>
       </c>
+      <c r="AE2">
+        <v>20</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>5</v>
+      </c>
+      <c r="AH2">
+        <v>0.25</v>
+      </c>
       <c r="AI2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AJ2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK2">
+        <v>18</v>
+      </c>
+      <c r="AL2">
+        <v>19</v>
+      </c>
+      <c r="AM2">
+        <v>9</v>
+      </c>
+      <c r="AN2">
+        <v>1.71</v>
+      </c>
+      <c r="AO2">
+        <v>9</v>
+      </c>
+      <c r="AP2">
+        <v>1.71</v>
+      </c>
+      <c r="AQ2">
+        <v>22.42</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>ORD_10001</v>
+      </c>
+      <c r="AU2" t="str">
+        <v>INV_10001</v>
+      </c>
+      <c r="AV2" t="str">
+        <v>AWB_50001</v>
+      </c>
+      <c r="AW2" t="str">
+        <v>2026-03-10 10:30:00</v>
+      </c>
+      <c r="AX2" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="AY2">
+        <v>2000</v>
+      </c>
+      <c r="AZ2">
+        <v>100</v>
+      </c>
+      <c r="BA2">
+        <v>342</v>
+      </c>
+      <c r="BB2">
+        <v>2242</v>
+      </c>
+      <c r="BC2">
+        <v>1500</v>
+      </c>
+      <c r="BD2">
+        <v>742</v>
+      </c>
+      <c r="BE2">
+        <v>120</v>
+      </c>
+      <c r="BF2" t="str">
+        <v>Sample order with payment</v>
+      </c>
+      <c r="BG2">
+        <v>100</v>
+      </c>
+      <c r="BH2">
+        <v>19</v>
+      </c>
+      <c r="BI2">
+        <v>100</v>
+      </c>
+      <c r="BJ2">
         <v>5</v>
       </c>
-      <c r="AL2">
-        <v>0.25</v>
-      </c>
-      <c r="AM2">
-        <v>5</v>
-      </c>
-      <c r="AN2">
-        <v>5</v>
-      </c>
-      <c r="AO2">
-        <v>18</v>
-      </c>
-      <c r="AP2">
-        <v>19</v>
-      </c>
-      <c r="AQ2">
+      <c r="BK2">
         <v>9</v>
       </c>
-      <c r="AR2">
-        <v>1.71</v>
-      </c>
-      <c r="AS2">
+      <c r="BL2">
+        <v>171</v>
+      </c>
+      <c r="BM2">
         <v>9</v>
       </c>
-      <c r="AT2">
-        <v>1.71</v>
-      </c>
-      <c r="AU2">
-        <v>22.42</v>
-      </c>
-      <c r="AV2">
+      <c r="BN2">
+        <v>171</v>
+      </c>
+      <c r="BO2">
         <v>0</v>
       </c>
-      <c r="AW2">
+      <c r="BP2">
         <v>0</v>
       </c>
-      <c r="AX2" t="str">
-        <v>ORD_10001</v>
-      </c>
-      <c r="AY2" t="str">
-        <v>INV_10001</v>
-      </c>
-      <c r="AZ2" t="str">
-        <v>AWB_50001</v>
-      </c>
-      <c r="BA2" t="str">
-        <v>2026-03-10 10:30:00</v>
-      </c>
-      <c r="BB2" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="BC2">
-        <v>2000</v>
-      </c>
-      <c r="BD2">
-        <v>100</v>
-      </c>
-      <c r="BE2">
+      <c r="BQ2">
         <v>342</v>
       </c>
-      <c r="BF2">
+      <c r="BR2">
         <v>2242</v>
       </c>
-      <c r="BG2">
+      <c r="BS2" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="BT2" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="BU2">
         <v>1500</v>
       </c>
-      <c r="BH2">
-        <v>742</v>
-      </c>
-      <c r="BI2">
-        <v>120</v>
-      </c>
-      <c r="BJ2" t="str">
-        <v>Sample order with payment</v>
-      </c>
-      <c r="BK2" t="str">
-        <v>LINE_1</v>
-      </c>
-      <c r="BL2">
-        <v>100</v>
-      </c>
-      <c r="BM2">
-        <v>19</v>
-      </c>
-      <c r="BN2">
-        <v>100</v>
-      </c>
-      <c r="BO2">
-        <v>5</v>
-      </c>
-      <c r="BP2">
-        <v>9</v>
-      </c>
-      <c r="BQ2">
-        <v>171</v>
-      </c>
-      <c r="BR2">
-        <v>9</v>
-      </c>
-      <c r="BS2">
-        <v>171</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>342</v>
-      </c>
-      <c r="BW2">
-        <v>2242</v>
-      </c>
-      <c r="BX2" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="BY2" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="BZ2">
-        <v>1500</v>
-      </c>
-      <c r="CA2" t="str">
+      <c r="BV2" t="str">
         <v>UPI123456789</v>
       </c>
     </row>
@@ -909,210 +879,195 @@
         <v>Ravi Kumar</v>
       </c>
       <c r="K3" t="str">
-        <v>EMP_1001</v>
+        <v>9876543210</v>
       </c>
       <c r="L3" t="str">
-        <v>EXT_SM_9001</v>
+        <v>SOUTH</v>
       </c>
       <c r="M3" t="str">
-        <v>9876543210</v>
+        <v>KARNATAKA</v>
       </c>
       <c r="N3" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="O3" t="str">
+        <v>OUT_0001</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Annapurna Stores</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="R3" t="str">
+        <v>29ABCDE1234F1Z5</v>
+      </c>
+      <c r="S3" t="str">
+        <v>12, 100 Feet Rd</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="U3" t="str">
+        <v>560038</v>
+      </c>
+      <c r="V3">
+        <v>12.9715987</v>
+      </c>
+      <c r="W3">
+        <v>77.6400001</v>
+      </c>
+      <c r="X3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Y3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Z3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="Q3" t="str">
-        <v>OUT_0001</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Annapurna Stores</v>
-      </c>
-      <c r="S3" t="str">
-        <v>9988776655</v>
-      </c>
-      <c r="T3" t="str">
-        <v>29ABCDE1234F1Z5</v>
-      </c>
-      <c r="U3" t="str">
-        <v>12, 100 Feet Rd</v>
-      </c>
-      <c r="V3" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="W3" t="str">
-        <v>560038</v>
-      </c>
-      <c r="X3">
-        <v>12.9715987</v>
-      </c>
-      <c r="Y3">
-        <v>77.6400001</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>SOUTH</v>
-      </c>
       <c r="AA3" t="str">
-        <v>KARNATAKA</v>
+        <v>Super Cola</v>
       </c>
       <c r="AB3" t="str">
-        <v>BENGALURU</v>
+        <v>SKU_COLA_500</v>
       </c>
       <c r="AC3" t="str">
-        <v>TOUT_0001</v>
+        <v>Super Cola 500ml</v>
       </c>
       <c r="AD3" t="str">
-        <v>BRAND_COLA</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>Super Cola</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>SKU_COLA_500</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>Super Cola 500ml</v>
-      </c>
-      <c r="AH3" t="str">
         <v>22021020</v>
       </c>
+      <c r="AE3">
+        <v>35</v>
+      </c>
+      <c r="AF3">
+        <v>2</v>
+      </c>
+      <c r="AG3">
+        <v>5.71</v>
+      </c>
+      <c r="AH3">
+        <v>0.5</v>
+      </c>
       <c r="AI3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="AJ3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK3">
-        <v>5.71</v>
+        <v>22</v>
       </c>
       <c r="AL3">
-        <v>0.5</v>
+        <v>33</v>
       </c>
       <c r="AM3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AN3">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="AO3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AP3">
+        <v>2.97</v>
+      </c>
+      <c r="AQ3">
+        <v>38.94</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>ORD_10001</v>
+      </c>
+      <c r="AU3" t="str">
+        <v>INV_10001</v>
+      </c>
+      <c r="AV3" t="str">
+        <v>AWB_50001</v>
+      </c>
+      <c r="AW3" t="str">
+        <v>2026-03-10 10:30:00</v>
+      </c>
+      <c r="AX3" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="AY3">
+        <v>2000</v>
+      </c>
+      <c r="AZ3">
+        <v>100</v>
+      </c>
+      <c r="BA3">
+        <v>342</v>
+      </c>
+      <c r="BB3">
+        <v>2242</v>
+      </c>
+      <c r="BC3">
+        <v>1500</v>
+      </c>
+      <c r="BD3">
+        <v>742</v>
+      </c>
+      <c r="BE3">
+        <v>120</v>
+      </c>
+      <c r="BF3" t="str">
+        <v>Second line of same order</v>
+      </c>
+      <c r="BG3">
+        <v>50</v>
+      </c>
+      <c r="BH3">
         <v>33</v>
       </c>
-      <c r="AQ3">
+      <c r="BI3">
+        <v>50</v>
+      </c>
+      <c r="BJ3">
+        <v>3.03</v>
+      </c>
+      <c r="BK3">
         <v>9</v>
       </c>
-      <c r="AR3">
-        <v>2.97</v>
-      </c>
-      <c r="AS3">
+      <c r="BL3">
+        <v>148.5</v>
+      </c>
+      <c r="BM3">
         <v>9</v>
       </c>
-      <c r="AT3">
-        <v>2.97</v>
-      </c>
-      <c r="AU3">
-        <v>38.94</v>
-      </c>
-      <c r="AV3">
+      <c r="BN3">
+        <v>148.5</v>
+      </c>
+      <c r="BO3">
         <v>0</v>
       </c>
-      <c r="AW3">
+      <c r="BP3">
         <v>0</v>
       </c>
-      <c r="AX3" t="str">
-        <v>ORD_10001</v>
-      </c>
-      <c r="AY3" t="str">
-        <v>INV_10001</v>
-      </c>
-      <c r="AZ3" t="str">
-        <v>AWB_50001</v>
-      </c>
-      <c r="BA3" t="str">
-        <v>2026-03-10 10:30:00</v>
-      </c>
-      <c r="BB3" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="BC3">
-        <v>2000</v>
-      </c>
-      <c r="BD3">
-        <v>100</v>
-      </c>
-      <c r="BE3">
-        <v>342</v>
-      </c>
-      <c r="BF3">
-        <v>2242</v>
-      </c>
-      <c r="BG3">
-        <v>1500</v>
-      </c>
-      <c r="BH3">
-        <v>742</v>
-      </c>
-      <c r="BI3">
-        <v>120</v>
-      </c>
-      <c r="BJ3" t="str">
-        <v>Second line of same order</v>
-      </c>
-      <c r="BK3" t="str">
-        <v>LINE_2</v>
-      </c>
-      <c r="BL3">
-        <v>50</v>
-      </c>
-      <c r="BM3">
-        <v>33</v>
-      </c>
-      <c r="BN3">
-        <v>50</v>
-      </c>
-      <c r="BO3">
-        <v>3.03</v>
-      </c>
-      <c r="BP3">
-        <v>9</v>
-      </c>
       <c r="BQ3">
-        <v>148.5</v>
+        <v>297</v>
       </c>
       <c r="BR3">
-        <v>9</v>
-      </c>
-      <c r="BS3">
-        <v>148.5</v>
-      </c>
-      <c r="BT3">
-        <v>0</v>
-      </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
-      <c r="BV3">
-        <v>297</v>
-      </c>
-      <c r="BW3">
         <v>1947</v>
       </c>
-      <c r="BX3" t="str">
+      <c r="BS3" t="str">
         <v/>
       </c>
-      <c r="BY3" t="str">
+      <c r="BT3" t="str">
         <v/>
       </c>
-      <c r="BZ3" t="str">
+      <c r="BU3" t="str">
         <v/>
       </c>
-      <c r="CA3" t="str">
+      <c r="BV3" t="str">
         <v/>
       </c>
     </row>
@@ -1148,216 +1103,201 @@
         <v>Meera Nair</v>
       </c>
       <c r="K4" t="str">
-        <v>EMP_1002</v>
+        <v>9123456780</v>
       </c>
       <c r="L4" t="str">
-        <v>EXT_SM_9002</v>
+        <v>SOUTH</v>
       </c>
       <c r="M4" t="str">
-        <v>9123456780</v>
+        <v>KARNATAKA</v>
       </c>
       <c r="N4" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="O4" t="str">
+        <v>OUT_0002</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Sri Ganesh Traders</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>9012345678</v>
+      </c>
+      <c r="R4" t="str">
+        <v>29ABCDE5678G1Z1</v>
+      </c>
+      <c r="S4" t="str">
+        <v>21, CMH Rd</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="U4" t="str">
+        <v>560038</v>
+      </c>
+      <c r="V4">
+        <v>12.975</v>
+      </c>
+      <c r="W4">
+        <v>77.642</v>
+      </c>
+      <c r="X4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Y4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Z4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="Q4" t="str">
-        <v>OUT_0002</v>
-      </c>
-      <c r="R4" t="str">
-        <v>Sri Ganesh Traders</v>
-      </c>
-      <c r="S4" t="str">
-        <v>9012345678</v>
-      </c>
-      <c r="T4" t="str">
-        <v>29ABCDE5678G1Z1</v>
-      </c>
-      <c r="U4" t="str">
-        <v>21, CMH Rd</v>
-      </c>
-      <c r="V4" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="W4" t="str">
-        <v>560038</v>
-      </c>
-      <c r="X4">
-        <v>12.975</v>
-      </c>
-      <c r="Y4">
-        <v>77.642</v>
-      </c>
-      <c r="Z4" t="str">
-        <v>SOUTH</v>
-      </c>
       <c r="AA4" t="str">
-        <v>KARNATAKA</v>
+        <v>Crispy Bites</v>
       </c>
       <c r="AB4" t="str">
-        <v>BENGALURU</v>
+        <v>SKU_SNACK_100</v>
       </c>
       <c r="AC4" t="str">
-        <v>TOUT_0002</v>
+        <v>Crispy Bites 100g</v>
       </c>
       <c r="AD4" t="str">
-        <v>BRAND_SNACKS</v>
-      </c>
-      <c r="AE4" t="str">
-        <v>Crispy Bites</v>
-      </c>
-      <c r="AF4" t="str">
-        <v>SKU_SNACK_100</v>
-      </c>
-      <c r="AG4" t="str">
-        <v>Crispy Bites 100g</v>
-      </c>
-      <c r="AH4" t="str">
         <v>19059040</v>
       </c>
+      <c r="AE4">
+        <v>25</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>4</v>
+      </c>
+      <c r="AH4">
+        <v>0.1</v>
+      </c>
       <c r="AI4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AJ4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AK4">
         <v>4</v>
       </c>
       <c r="AL4">
-        <v>0.1</v>
+        <v>22</v>
       </c>
       <c r="AM4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>8</v>
+        <v>1.32</v>
       </c>
       <c r="AO4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP4">
+        <v>1.32</v>
+      </c>
+      <c r="AQ4">
+        <v>24.64</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>ORD_10002</v>
+      </c>
+      <c r="AU4" t="str">
+        <v>INV_10002</v>
+      </c>
+      <c r="AV4" t="str">
+        <v>AWB_50002</v>
+      </c>
+      <c r="AW4" t="str">
+        <v>2026-03-12 16:10:00</v>
+      </c>
+      <c r="AX4" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="AY4">
+        <v>1760</v>
+      </c>
+      <c r="AZ4">
+        <v>80</v>
+      </c>
+      <c r="BA4">
+        <v>201.6</v>
+      </c>
+      <c r="BB4">
+        <v>1881.6</v>
+      </c>
+      <c r="BC4">
+        <v>1000</v>
+      </c>
+      <c r="BD4">
+        <v>881.6</v>
+      </c>
+      <c r="BE4">
+        <v>95</v>
+      </c>
+      <c r="BF4" t="str">
+        <v>Second sample order</v>
+      </c>
+      <c r="BG4">
+        <v>80</v>
+      </c>
+      <c r="BH4">
         <v>22</v>
       </c>
-      <c r="AQ4">
+      <c r="BI4">
+        <v>80</v>
+      </c>
+      <c r="BJ4">
+        <v>4.55</v>
+      </c>
+      <c r="BK4">
         <v>6</v>
       </c>
-      <c r="AR4">
-        <v>1.32</v>
-      </c>
-      <c r="AS4">
+      <c r="BL4">
+        <v>100.8</v>
+      </c>
+      <c r="BM4">
         <v>6</v>
       </c>
-      <c r="AT4">
-        <v>1.32</v>
-      </c>
-      <c r="AU4">
-        <v>24.64</v>
-      </c>
-      <c r="AV4">
+      <c r="BN4">
+        <v>100.8</v>
+      </c>
+      <c r="BO4">
         <v>0</v>
       </c>
-      <c r="AW4">
+      <c r="BP4">
         <v>0</v>
       </c>
-      <c r="AX4" t="str">
-        <v>ORD_10002</v>
-      </c>
-      <c r="AY4" t="str">
-        <v>INV_10002</v>
-      </c>
-      <c r="AZ4" t="str">
-        <v>AWB_50002</v>
-      </c>
-      <c r="BA4" t="str">
-        <v>2026-03-12 16:10:00</v>
-      </c>
-      <c r="BB4" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="BC4">
-        <v>1760</v>
-      </c>
-      <c r="BD4">
-        <v>80</v>
-      </c>
-      <c r="BE4">
+      <c r="BQ4">
         <v>201.6</v>
       </c>
-      <c r="BF4">
+      <c r="BR4">
         <v>1881.6</v>
       </c>
-      <c r="BG4">
+      <c r="BS4" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="BT4" t="str">
+        <v>CASH</v>
+      </c>
+      <c r="BU4">
         <v>1000</v>
       </c>
-      <c r="BH4">
-        <v>881.6</v>
-      </c>
-      <c r="BI4">
-        <v>95</v>
-      </c>
-      <c r="BJ4" t="str">
-        <v>Second sample order</v>
-      </c>
-      <c r="BK4" t="str">
-        <v>LINE_1</v>
-      </c>
-      <c r="BL4">
-        <v>80</v>
-      </c>
-      <c r="BM4">
-        <v>22</v>
-      </c>
-      <c r="BN4">
-        <v>80</v>
-      </c>
-      <c r="BO4">
-        <v>4.55</v>
-      </c>
-      <c r="BP4">
-        <v>6</v>
-      </c>
-      <c r="BQ4">
-        <v>100.8</v>
-      </c>
-      <c r="BR4">
-        <v>6</v>
-      </c>
-      <c r="BS4">
-        <v>100.8</v>
-      </c>
-      <c r="BT4">
-        <v>0</v>
-      </c>
-      <c r="BU4">
-        <v>0</v>
-      </c>
-      <c r="BV4">
-        <v>201.6</v>
-      </c>
-      <c r="BW4">
-        <v>1881.6</v>
-      </c>
-      <c r="BX4" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="BY4" t="str">
-        <v>CASH</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="str">
+      <c r="BV4" t="str">
         <v>CASH001</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CA4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BV4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/templates/customer-data-template.xlsx
+++ b/docs/templates/customer-data-template.xlsx
@@ -397,229 +397,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV4"/>
+  <dimension ref="A1:BS4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.no</v>
       </c>
       <c r="B1" t="str">
-        <v>distributors.distributor_code</v>
+        <v>distributors.distributor_name</v>
       </c>
       <c r="C1" t="str">
-        <v>distributors.distributor_name</v>
+        <v>distributors.zone</v>
       </c>
       <c r="D1" t="str">
-        <v>distributors.zone</v>
+        <v>distributors.region</v>
       </c>
       <c r="E1" t="str">
-        <v>distributors.region</v>
+        <v>distributors.area</v>
       </c>
       <c r="F1" t="str">
-        <v>distributors.area</v>
+        <v>beats.beat_name</v>
       </c>
       <c r="G1" t="str">
-        <v>beats.beat_code</v>
+        <v>salesmen.salesman_name</v>
       </c>
       <c r="H1" t="str">
-        <v>beats.beat_name</v>
+        <v>salesmen.phone_number</v>
       </c>
       <c r="I1" t="str">
-        <v>salesmen.salesman_code</v>
+        <v>salesmen.zone</v>
       </c>
       <c r="J1" t="str">
-        <v>salesmen.salesman_name</v>
+        <v>salesmen.region</v>
       </c>
       <c r="K1" t="str">
-        <v>salesmen.phone_number</v>
+        <v>salesmen.area</v>
       </c>
       <c r="L1" t="str">
-        <v>salesmen.zone</v>
+        <v>outlets.external_outlet_code</v>
       </c>
       <c r="M1" t="str">
-        <v>salesmen.region</v>
+        <v>outlets.outlet_name</v>
       </c>
       <c r="N1" t="str">
-        <v>salesmen.area</v>
+        <v>outlets.mobile_number</v>
       </c>
       <c r="O1" t="str">
-        <v>outlets.external_outlet_code</v>
+        <v>outlets.gst_number</v>
       </c>
       <c r="P1" t="str">
-        <v>outlets.outlet_name</v>
+        <v>outlets.address_line1</v>
       </c>
       <c r="Q1" t="str">
-        <v>outlets.mobile_number</v>
+        <v>outlets.address_line2</v>
       </c>
       <c r="R1" t="str">
-        <v>outlets.gst_number</v>
+        <v>outlets.pincode</v>
       </c>
       <c r="S1" t="str">
-        <v>outlets.address_line1</v>
+        <v>outlets.latitude</v>
       </c>
       <c r="T1" t="str">
-        <v>outlets.address_line2</v>
+        <v>outlets.longitude</v>
       </c>
       <c r="U1" t="str">
-        <v>outlets.pincode</v>
+        <v>outlets.zone</v>
       </c>
       <c r="V1" t="str">
-        <v>outlets.latitude</v>
+        <v>outlets.region</v>
       </c>
       <c r="W1" t="str">
-        <v>outlets.longitude</v>
+        <v>outlets.area</v>
       </c>
       <c r="X1" t="str">
-        <v>outlets.zone</v>
+        <v>brands.brand_name</v>
       </c>
       <c r="Y1" t="str">
-        <v>outlets.region</v>
+        <v>skus.sku_code</v>
       </c>
       <c r="Z1" t="str">
-        <v>outlets.area</v>
+        <v>skus.name</v>
       </c>
       <c r="AA1" t="str">
-        <v>brands.brand_name</v>
+        <v>skus.hsn_code</v>
       </c>
       <c r="AB1" t="str">
-        <v>skus.sku_code</v>
+        <v>skus.mrp</v>
       </c>
       <c r="AC1" t="str">
-        <v>skus.name</v>
+        <v>skus.discount_amount</v>
       </c>
       <c r="AD1" t="str">
-        <v>skus.hsn_code</v>
+        <v>skus.discount_percent</v>
       </c>
       <c r="AE1" t="str">
-        <v>skus.mrp</v>
+        <v>skus.weight</v>
       </c>
       <c r="AF1" t="str">
-        <v>skus.discount_amount</v>
+        <v>skus.length_cm</v>
       </c>
       <c r="AG1" t="str">
-        <v>skus.discount_percent</v>
+        <v>skus.width_cm</v>
       </c>
       <c r="AH1" t="str">
-        <v>skus.weight</v>
+        <v>skus.height_cm</v>
       </c>
       <c r="AI1" t="str">
-        <v>skus.length_cm</v>
+        <v>skus.rate</v>
       </c>
       <c r="AJ1" t="str">
-        <v>skus.width_cm</v>
+        <v>skus.sgst_percent</v>
       </c>
       <c r="AK1" t="str">
-        <v>skus.height_cm</v>
+        <v>skus.sgst_amount</v>
       </c>
       <c r="AL1" t="str">
-        <v>skus.rate</v>
+        <v>skus.cgst_percent</v>
       </c>
       <c r="AM1" t="str">
-        <v>skus.sgst_percent</v>
+        <v>skus.cgst_amount</v>
       </c>
       <c r="AN1" t="str">
-        <v>skus.sgst_amount</v>
+        <v>skus.amount</v>
       </c>
       <c r="AO1" t="str">
-        <v>skus.cgst_percent</v>
+        <v>skus.igst_percent</v>
       </c>
       <c r="AP1" t="str">
-        <v>skus.cgst_amount</v>
+        <v>skus.igst_amount</v>
       </c>
       <c r="AQ1" t="str">
-        <v>skus.amount</v>
+        <v>sales_orders.external_order_id</v>
       </c>
       <c r="AR1" t="str">
-        <v>skus.igst_percent</v>
+        <v>sales_orders.external_invoice_no</v>
       </c>
       <c r="AS1" t="str">
-        <v>skus.igst_amount</v>
+        <v>sales_orders.external_awb_no</v>
       </c>
       <c r="AT1" t="str">
-        <v>sales_orders.external_order_id</v>
+        <v>sales_orders.order_punched_at</v>
       </c>
       <c r="AU1" t="str">
-        <v>sales_orders.external_invoice_no</v>
+        <v>sales_orders.order_sale_date</v>
       </c>
       <c r="AV1" t="str">
-        <v>sales_orders.external_awb_no</v>
+        <v>sales_orders.gross_amount</v>
       </c>
       <c r="AW1" t="str">
-        <v>sales_orders.order_punched_at</v>
+        <v>sales_orders.discount_amount</v>
       </c>
       <c r="AX1" t="str">
-        <v>sales_orders.order_sale_date</v>
+        <v>sales_orders.tax_amount</v>
       </c>
       <c r="AY1" t="str">
-        <v>sales_orders.gross_amount</v>
+        <v>sales_orders.net_amount</v>
       </c>
       <c r="AZ1" t="str">
-        <v>sales_orders.discount_amount</v>
+        <v>sales_orders.collections_amount</v>
       </c>
       <c r="BA1" t="str">
-        <v>sales_orders.tax_amount</v>
+        <v>sales_orders.outstanding_amount</v>
       </c>
       <c r="BB1" t="str">
-        <v>sales_orders.net_amount</v>
+        <v>sales_orders.decided_margin_amount</v>
       </c>
       <c r="BC1" t="str">
-        <v>sales_orders.collections_amount</v>
+        <v>sales_orders.remarks</v>
       </c>
       <c r="BD1" t="str">
-        <v>sales_orders.outstanding_amount</v>
+        <v>sales_order_items.ordered_quantity</v>
       </c>
       <c r="BE1" t="str">
-        <v>sales_orders.decided_margin_amount</v>
+        <v>sales_order_items.rate</v>
       </c>
       <c r="BF1" t="str">
-        <v>sales_orders.remarks</v>
+        <v>sales_order_items.discount_amount</v>
       </c>
       <c r="BG1" t="str">
-        <v>sales_order_items.ordered_quantity</v>
+        <v>sales_order_items.discount_percent</v>
       </c>
       <c r="BH1" t="str">
-        <v>sales_order_items.rate</v>
+        <v>sales_order_items.sgst_percent</v>
       </c>
       <c r="BI1" t="str">
-        <v>sales_order_items.discount_amount</v>
+        <v>sales_order_items.sgst_amount</v>
       </c>
       <c r="BJ1" t="str">
-        <v>sales_order_items.discount_percent</v>
+        <v>sales_order_items.cgst_percent</v>
       </c>
       <c r="BK1" t="str">
-        <v>sales_order_items.sgst_percent</v>
+        <v>sales_order_items.cgst_amount</v>
       </c>
       <c r="BL1" t="str">
-        <v>sales_order_items.sgst_amount</v>
+        <v>sales_order_items.igst_percent</v>
       </c>
       <c r="BM1" t="str">
-        <v>sales_order_items.cgst_percent</v>
+        <v>sales_order_items.igst_amount</v>
       </c>
       <c r="BN1" t="str">
-        <v>sales_order_items.cgst_amount</v>
+        <v>sales_order_items.tax_amount</v>
       </c>
       <c r="BO1" t="str">
-        <v>sales_order_items.igst_percent</v>
+        <v>sales_order_items.amount</v>
       </c>
       <c r="BP1" t="str">
-        <v>sales_order_items.igst_amount</v>
+        <v>order_payments.payment_date</v>
       </c>
       <c r="BQ1" t="str">
-        <v>sales_order_items.tax_amount</v>
+        <v>order_payments.payment_mode</v>
       </c>
       <c r="BR1" t="str">
-        <v>sales_order_items.amount</v>
+        <v>order_payments.amount</v>
       </c>
       <c r="BS1" t="str">
-        <v>order_payments.payment_date</v>
-      </c>
-      <c r="BT1" t="str">
-        <v>order_payments.payment_mode</v>
-      </c>
-      <c r="BU1" t="str">
-        <v>order_payments.amount</v>
-      </c>
-      <c r="BV1" t="str">
         <v>order_payments.external_ref</v>
       </c>
     </row>
@@ -628,222 +619,213 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>DIST_SOUTH_01</v>
+        <v>South Distribution LLP</v>
       </c>
       <c r="C2" t="str">
-        <v>South Distribution LLP</v>
+        <v>SOUTH</v>
       </c>
       <c r="D2" t="str">
+        <v>KARNATAKA</v>
+      </c>
+      <c r="E2" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Indiranagar Morning Beat</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Ravi Kumar</v>
+      </c>
+      <c r="H2" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="I2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="E2" t="str">
+      <c r="J2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="F2" t="str">
+      <c r="K2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="G2" t="str">
-        <v>BEAT_BLR_01</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Indiranagar Morning Beat</v>
-      </c>
-      <c r="I2" t="str">
-        <v>SM_001</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Ravi Kumar</v>
-      </c>
-      <c r="K2" t="str">
-        <v>9876543210</v>
-      </c>
       <c r="L2" t="str">
+        <v>OUT_0001</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Annapurna Stores</v>
+      </c>
+      <c r="N2" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="O2" t="str">
+        <v>29ABCDE1234F1Z5</v>
+      </c>
+      <c r="P2" t="str">
+        <v>12, 100 Feet Rd</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="R2" t="str">
+        <v>560038</v>
+      </c>
+      <c r="S2">
+        <v>12.9715987</v>
+      </c>
+      <c r="T2">
+        <v>77.6400001</v>
+      </c>
+      <c r="U2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="M2" t="str">
+      <c r="V2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="N2" t="str">
+      <c r="W2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="O2" t="str">
-        <v>OUT_0001</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Annapurna Stores</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>9988776655</v>
-      </c>
-      <c r="R2" t="str">
-        <v>29ABCDE1234F1Z5</v>
-      </c>
-      <c r="S2" t="str">
-        <v>12, 100 Feet Rd</v>
-      </c>
-      <c r="T2" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="U2" t="str">
-        <v>560038</v>
-      </c>
-      <c r="V2">
-        <v>12.9715987</v>
-      </c>
-      <c r="W2">
-        <v>77.6400001</v>
-      </c>
       <c r="X2" t="str">
-        <v>SOUTH</v>
+        <v>Super Cola</v>
       </c>
       <c r="Y2" t="str">
-        <v>KARNATAKA</v>
+        <v>SKU_COLA_250</v>
       </c>
       <c r="Z2" t="str">
-        <v>BENGALURU</v>
+        <v>Super Cola 250ml</v>
       </c>
       <c r="AA2" t="str">
-        <v>Super Cola</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>SKU_COLA_250</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Super Cola 250ml</v>
-      </c>
-      <c r="AD2" t="str">
         <v>22021020</v>
       </c>
+      <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>5</v>
+      </c>
       <c r="AE2">
-        <v>20</v>
+        <v>0.25</v>
       </c>
       <c r="AF2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG2">
         <v>5</v>
       </c>
       <c r="AH2">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="AI2">
+        <v>19</v>
+      </c>
+      <c r="AJ2">
+        <v>9</v>
+      </c>
+      <c r="AK2">
+        <v>1.71</v>
+      </c>
+      <c r="AL2">
+        <v>9</v>
+      </c>
+      <c r="AM2">
+        <v>1.71</v>
+      </c>
+      <c r="AN2">
+        <v>22.42</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>ORD_10001</v>
+      </c>
+      <c r="AR2" t="str">
+        <v>INV_10001</v>
+      </c>
+      <c r="AS2" t="str">
+        <v>AWB_50001</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>2026-03-10 10:30:00</v>
+      </c>
+      <c r="AU2" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="AV2">
+        <v>2000</v>
+      </c>
+      <c r="AW2">
+        <v>100</v>
+      </c>
+      <c r="AX2">
+        <v>342</v>
+      </c>
+      <c r="AY2">
+        <v>2242</v>
+      </c>
+      <c r="AZ2">
+        <v>1500</v>
+      </c>
+      <c r="BA2">
+        <v>742</v>
+      </c>
+      <c r="BB2">
+        <v>120</v>
+      </c>
+      <c r="BC2" t="str">
+        <v>Sample order with payment</v>
+      </c>
+      <c r="BD2">
+        <v>100</v>
+      </c>
+      <c r="BE2">
+        <v>19</v>
+      </c>
+      <c r="BF2">
+        <v>100</v>
+      </c>
+      <c r="BG2">
         <v>5</v>
       </c>
-      <c r="AJ2">
-        <v>5</v>
-      </c>
-      <c r="AK2">
-        <v>18</v>
-      </c>
-      <c r="AL2">
-        <v>19</v>
-      </c>
-      <c r="AM2">
+      <c r="BH2">
         <v>9</v>
       </c>
-      <c r="AN2">
-        <v>1.71</v>
-      </c>
-      <c r="AO2">
+      <c r="BI2">
+        <v>171</v>
+      </c>
+      <c r="BJ2">
         <v>9</v>
       </c>
-      <c r="AP2">
-        <v>1.71</v>
-      </c>
-      <c r="AQ2">
-        <v>22.42</v>
-      </c>
-      <c r="AR2">
+      <c r="BK2">
+        <v>171</v>
+      </c>
+      <c r="BL2">
         <v>0</v>
       </c>
-      <c r="AS2">
+      <c r="BM2">
         <v>0</v>
       </c>
-      <c r="AT2" t="str">
-        <v>ORD_10001</v>
-      </c>
-      <c r="AU2" t="str">
-        <v>INV_10001</v>
-      </c>
-      <c r="AV2" t="str">
-        <v>AWB_50001</v>
-      </c>
-      <c r="AW2" t="str">
-        <v>2026-03-10 10:30:00</v>
-      </c>
-      <c r="AX2" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="AY2">
-        <v>2000</v>
-      </c>
-      <c r="AZ2">
-        <v>100</v>
-      </c>
-      <c r="BA2">
+      <c r="BN2">
         <v>342</v>
       </c>
-      <c r="BB2">
+      <c r="BO2">
         <v>2242</v>
       </c>
-      <c r="BC2">
+      <c r="BP2" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="BQ2" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="BR2">
         <v>1500</v>
       </c>
-      <c r="BD2">
-        <v>742</v>
-      </c>
-      <c r="BE2">
-        <v>120</v>
-      </c>
-      <c r="BF2" t="str">
-        <v>Sample order with payment</v>
-      </c>
-      <c r="BG2">
-        <v>100</v>
-      </c>
-      <c r="BH2">
-        <v>19</v>
-      </c>
-      <c r="BI2">
-        <v>100</v>
-      </c>
-      <c r="BJ2">
-        <v>5</v>
-      </c>
-      <c r="BK2">
-        <v>9</v>
-      </c>
-      <c r="BL2">
-        <v>171</v>
-      </c>
-      <c r="BM2">
-        <v>9</v>
-      </c>
-      <c r="BN2">
-        <v>171</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>342</v>
-      </c>
-      <c r="BR2">
-        <v>2242</v>
-      </c>
       <c r="BS2" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="BT2" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="BU2">
-        <v>1500</v>
-      </c>
-      <c r="BV2" t="str">
         <v>UPI123456789</v>
       </c>
     </row>
@@ -852,222 +834,213 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>DIST_SOUTH_01</v>
+        <v>South Distribution LLP</v>
       </c>
       <c r="C3" t="str">
-        <v>South Distribution LLP</v>
+        <v>SOUTH</v>
       </c>
       <c r="D3" t="str">
+        <v>KARNATAKA</v>
+      </c>
+      <c r="E3" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Indiranagar Morning Beat</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Ravi Kumar</v>
+      </c>
+      <c r="H3" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="I3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="E3" t="str">
+      <c r="J3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="F3" t="str">
+      <c r="K3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="G3" t="str">
-        <v>BEAT_BLR_01</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Indiranagar Morning Beat</v>
-      </c>
-      <c r="I3" t="str">
-        <v>SM_001</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Ravi Kumar</v>
-      </c>
-      <c r="K3" t="str">
-        <v>9876543210</v>
-      </c>
       <c r="L3" t="str">
+        <v>OUT_0001</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Annapurna Stores</v>
+      </c>
+      <c r="N3" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="O3" t="str">
+        <v>29ABCDE1234F1Z5</v>
+      </c>
+      <c r="P3" t="str">
+        <v>12, 100 Feet Rd</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="R3" t="str">
+        <v>560038</v>
+      </c>
+      <c r="S3">
+        <v>12.9715987</v>
+      </c>
+      <c r="T3">
+        <v>77.6400001</v>
+      </c>
+      <c r="U3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="M3" t="str">
+      <c r="V3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="N3" t="str">
+      <c r="W3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="O3" t="str">
-        <v>OUT_0001</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Annapurna Stores</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>9988776655</v>
-      </c>
-      <c r="R3" t="str">
-        <v>29ABCDE1234F1Z5</v>
-      </c>
-      <c r="S3" t="str">
-        <v>12, 100 Feet Rd</v>
-      </c>
-      <c r="T3" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="U3" t="str">
-        <v>560038</v>
-      </c>
-      <c r="V3">
-        <v>12.9715987</v>
-      </c>
-      <c r="W3">
-        <v>77.6400001</v>
-      </c>
       <c r="X3" t="str">
-        <v>SOUTH</v>
+        <v>Super Cola</v>
       </c>
       <c r="Y3" t="str">
-        <v>KARNATAKA</v>
+        <v>SKU_COLA_500</v>
       </c>
       <c r="Z3" t="str">
-        <v>BENGALURU</v>
+        <v>Super Cola 500ml</v>
       </c>
       <c r="AA3" t="str">
-        <v>Super Cola</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>SKU_COLA_500</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Super Cola 500ml</v>
-      </c>
-      <c r="AD3" t="str">
         <v>22021020</v>
       </c>
+      <c r="AB3">
+        <v>35</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AD3">
+        <v>5.71</v>
+      </c>
       <c r="AE3">
-        <v>35</v>
+        <v>0.5</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG3">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="AH3">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="AJ3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>2.97</v>
       </c>
       <c r="AL3">
+        <v>9</v>
+      </c>
+      <c r="AM3">
+        <v>2.97</v>
+      </c>
+      <c r="AN3">
+        <v>38.94</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v>ORD_10001</v>
+      </c>
+      <c r="AR3" t="str">
+        <v>INV_10001</v>
+      </c>
+      <c r="AS3" t="str">
+        <v>AWB_50001</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>2026-03-10 10:30:00</v>
+      </c>
+      <c r="AU3" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="AV3">
+        <v>2000</v>
+      </c>
+      <c r="AW3">
+        <v>100</v>
+      </c>
+      <c r="AX3">
+        <v>342</v>
+      </c>
+      <c r="AY3">
+        <v>2242</v>
+      </c>
+      <c r="AZ3">
+        <v>1500</v>
+      </c>
+      <c r="BA3">
+        <v>742</v>
+      </c>
+      <c r="BB3">
+        <v>120</v>
+      </c>
+      <c r="BC3" t="str">
+        <v>Second line of same order</v>
+      </c>
+      <c r="BD3">
+        <v>50</v>
+      </c>
+      <c r="BE3">
         <v>33</v>
       </c>
-      <c r="AM3">
+      <c r="BF3">
+        <v>50</v>
+      </c>
+      <c r="BG3">
+        <v>3.03</v>
+      </c>
+      <c r="BH3">
         <v>9</v>
       </c>
-      <c r="AN3">
-        <v>2.97</v>
-      </c>
-      <c r="AO3">
+      <c r="BI3">
+        <v>148.5</v>
+      </c>
+      <c r="BJ3">
         <v>9</v>
       </c>
-      <c r="AP3">
-        <v>2.97</v>
-      </c>
-      <c r="AQ3">
-        <v>38.94</v>
-      </c>
-      <c r="AR3">
+      <c r="BK3">
+        <v>148.5</v>
+      </c>
+      <c r="BL3">
         <v>0</v>
       </c>
-      <c r="AS3">
+      <c r="BM3">
         <v>0</v>
       </c>
-      <c r="AT3" t="str">
-        <v>ORD_10001</v>
-      </c>
-      <c r="AU3" t="str">
-        <v>INV_10001</v>
-      </c>
-      <c r="AV3" t="str">
-        <v>AWB_50001</v>
-      </c>
-      <c r="AW3" t="str">
-        <v>2026-03-10 10:30:00</v>
-      </c>
-      <c r="AX3" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="AY3">
-        <v>2000</v>
-      </c>
-      <c r="AZ3">
-        <v>100</v>
-      </c>
-      <c r="BA3">
-        <v>342</v>
-      </c>
-      <c r="BB3">
-        <v>2242</v>
-      </c>
-      <c r="BC3">
-        <v>1500</v>
-      </c>
-      <c r="BD3">
-        <v>742</v>
-      </c>
-      <c r="BE3">
-        <v>120</v>
-      </c>
-      <c r="BF3" t="str">
-        <v>Second line of same order</v>
-      </c>
-      <c r="BG3">
-        <v>50</v>
-      </c>
-      <c r="BH3">
-        <v>33</v>
-      </c>
-      <c r="BI3">
-        <v>50</v>
-      </c>
-      <c r="BJ3">
-        <v>3.03</v>
-      </c>
-      <c r="BK3">
-        <v>9</v>
-      </c>
-      <c r="BL3">
-        <v>148.5</v>
-      </c>
-      <c r="BM3">
-        <v>9</v>
-      </c>
       <c r="BN3">
-        <v>148.5</v>
+        <v>297</v>
       </c>
       <c r="BO3">
-        <v>0</v>
-      </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>297</v>
-      </c>
-      <c r="BR3">
         <v>1947</v>
       </c>
+      <c r="BP3" t="str">
+        <v/>
+      </c>
+      <c r="BQ3" t="str">
+        <v/>
+      </c>
+      <c r="BR3" t="str">
+        <v/>
+      </c>
       <c r="BS3" t="str">
-        <v/>
-      </c>
-      <c r="BT3" t="str">
-        <v/>
-      </c>
-      <c r="BU3" t="str">
-        <v/>
-      </c>
-      <c r="BV3" t="str">
         <v/>
       </c>
     </row>
@@ -1076,228 +1049,219 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>DIST_SOUTH_01</v>
+        <v>South Distribution LLP</v>
       </c>
       <c r="C4" t="str">
-        <v>South Distribution LLP</v>
+        <v>SOUTH</v>
       </c>
       <c r="D4" t="str">
+        <v>KARNATAKA</v>
+      </c>
+      <c r="E4" t="str">
+        <v>BENGALURU</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Domlur Evening Beat</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Meera Nair</v>
+      </c>
+      <c r="H4" t="str">
+        <v>9123456780</v>
+      </c>
+      <c r="I4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="E4" t="str">
+      <c r="J4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="F4" t="str">
+      <c r="K4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="G4" t="str">
-        <v>BEAT_BLR_02</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Domlur Evening Beat</v>
-      </c>
-      <c r="I4" t="str">
-        <v>SM_002</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Meera Nair</v>
-      </c>
-      <c r="K4" t="str">
-        <v>9123456780</v>
-      </c>
       <c r="L4" t="str">
+        <v>OUT_0002</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Sri Ganesh Traders</v>
+      </c>
+      <c r="N4" t="str">
+        <v>9012345678</v>
+      </c>
+      <c r="O4" t="str">
+        <v>29ABCDE5678G1Z1</v>
+      </c>
+      <c r="P4" t="str">
+        <v>21, CMH Rd</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Indiranagar</v>
+      </c>
+      <c r="R4" t="str">
+        <v>560038</v>
+      </c>
+      <c r="S4">
+        <v>12.975</v>
+      </c>
+      <c r="T4">
+        <v>77.642</v>
+      </c>
+      <c r="U4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="M4" t="str">
+      <c r="V4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="N4" t="str">
+      <c r="W4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="O4" t="str">
-        <v>OUT_0002</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Sri Ganesh Traders</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>9012345678</v>
-      </c>
-      <c r="R4" t="str">
-        <v>29ABCDE5678G1Z1</v>
-      </c>
-      <c r="S4" t="str">
-        <v>21, CMH Rd</v>
-      </c>
-      <c r="T4" t="str">
-        <v>Indiranagar</v>
-      </c>
-      <c r="U4" t="str">
-        <v>560038</v>
-      </c>
-      <c r="V4">
-        <v>12.975</v>
-      </c>
-      <c r="W4">
-        <v>77.642</v>
-      </c>
       <c r="X4" t="str">
-        <v>SOUTH</v>
+        <v>Crispy Bites</v>
       </c>
       <c r="Y4" t="str">
-        <v>KARNATAKA</v>
+        <v>SKU_SNACK_100</v>
       </c>
       <c r="Z4" t="str">
-        <v>BENGALURU</v>
+        <v>Crispy Bites 100g</v>
       </c>
       <c r="AA4" t="str">
-        <v>Crispy Bites</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>SKU_SNACK_100</v>
-      </c>
-      <c r="AC4" t="str">
-        <v>Crispy Bites 100g</v>
-      </c>
-      <c r="AD4" t="str">
         <v>19059040</v>
       </c>
+      <c r="AB4">
+        <v>25</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>4</v>
+      </c>
       <c r="AE4">
-        <v>25</v>
+        <v>0.1</v>
       </c>
       <c r="AF4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AG4">
+        <v>8</v>
+      </c>
+      <c r="AH4">
         <v>4</v>
       </c>
-      <c r="AH4">
-        <v>0.1</v>
-      </c>
       <c r="AI4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AJ4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK4">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="AL4">
+        <v>6</v>
+      </c>
+      <c r="AM4">
+        <v>1.32</v>
+      </c>
+      <c r="AN4">
+        <v>24.64</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="str">
+        <v>ORD_10002</v>
+      </c>
+      <c r="AR4" t="str">
+        <v>INV_10002</v>
+      </c>
+      <c r="AS4" t="str">
+        <v>AWB_50002</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>2026-03-12 16:10:00</v>
+      </c>
+      <c r="AU4" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="AV4">
+        <v>1760</v>
+      </c>
+      <c r="AW4">
+        <v>80</v>
+      </c>
+      <c r="AX4">
+        <v>201.6</v>
+      </c>
+      <c r="AY4">
+        <v>1881.6</v>
+      </c>
+      <c r="AZ4">
+        <v>1000</v>
+      </c>
+      <c r="BA4">
+        <v>881.6</v>
+      </c>
+      <c r="BB4">
+        <v>95</v>
+      </c>
+      <c r="BC4" t="str">
+        <v>Second sample order</v>
+      </c>
+      <c r="BD4">
+        <v>80</v>
+      </c>
+      <c r="BE4">
         <v>22</v>
       </c>
-      <c r="AM4">
+      <c r="BF4">
+        <v>80</v>
+      </c>
+      <c r="BG4">
+        <v>4.55</v>
+      </c>
+      <c r="BH4">
         <v>6</v>
       </c>
-      <c r="AN4">
-        <v>1.32</v>
-      </c>
-      <c r="AO4">
+      <c r="BI4">
+        <v>100.8</v>
+      </c>
+      <c r="BJ4">
         <v>6</v>
       </c>
-      <c r="AP4">
-        <v>1.32</v>
-      </c>
-      <c r="AQ4">
-        <v>24.64</v>
-      </c>
-      <c r="AR4">
+      <c r="BK4">
+        <v>100.8</v>
+      </c>
+      <c r="BL4">
         <v>0</v>
       </c>
-      <c r="AS4">
+      <c r="BM4">
         <v>0</v>
       </c>
-      <c r="AT4" t="str">
-        <v>ORD_10002</v>
-      </c>
-      <c r="AU4" t="str">
-        <v>INV_10002</v>
-      </c>
-      <c r="AV4" t="str">
-        <v>AWB_50002</v>
-      </c>
-      <c r="AW4" t="str">
-        <v>2026-03-12 16:10:00</v>
-      </c>
-      <c r="AX4" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="AY4">
-        <v>1760</v>
-      </c>
-      <c r="AZ4">
-        <v>80</v>
-      </c>
-      <c r="BA4">
+      <c r="BN4">
         <v>201.6</v>
       </c>
-      <c r="BB4">
+      <c r="BO4">
         <v>1881.6</v>
       </c>
-      <c r="BC4">
+      <c r="BP4" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="BQ4" t="str">
+        <v>CASH</v>
+      </c>
+      <c r="BR4">
         <v>1000</v>
       </c>
-      <c r="BD4">
-        <v>881.6</v>
-      </c>
-      <c r="BE4">
-        <v>95</v>
-      </c>
-      <c r="BF4" t="str">
-        <v>Second sample order</v>
-      </c>
-      <c r="BG4">
-        <v>80</v>
-      </c>
-      <c r="BH4">
-        <v>22</v>
-      </c>
-      <c r="BI4">
-        <v>80</v>
-      </c>
-      <c r="BJ4">
-        <v>4.55</v>
-      </c>
-      <c r="BK4">
-        <v>6</v>
-      </c>
-      <c r="BL4">
-        <v>100.8</v>
-      </c>
-      <c r="BM4">
-        <v>6</v>
-      </c>
-      <c r="BN4">
-        <v>100.8</v>
-      </c>
-      <c r="BO4">
-        <v>0</v>
-      </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>201.6</v>
-      </c>
-      <c r="BR4">
-        <v>1881.6</v>
-      </c>
       <c r="BS4" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="BT4" t="str">
-        <v>CASH</v>
-      </c>
-      <c r="BU4">
-        <v>1000</v>
-      </c>
-      <c r="BV4" t="str">
         <v>CASH001</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BV4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BS4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/templates/customer-data-template.xlsx
+++ b/docs/templates/customer-data-template.xlsx
@@ -397,220 +397,244 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:CA4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.no</v>
       </c>
       <c r="B1" t="str">
+        <v>distributors.distributor_code</v>
+      </c>
+      <c r="C1" t="str">
         <v>distributors.distributor_name</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>distributors.zone</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>distributors.region</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>distributors.area</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>beats.beat_code</v>
+      </c>
+      <c r="H1" t="str">
         <v>beats.beat_name</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
+        <v>salesmen.salesman_code</v>
+      </c>
+      <c r="J1" t="str">
         <v>salesmen.salesman_name</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
+        <v>salesmen.employee_code</v>
+      </c>
+      <c r="L1" t="str">
+        <v>salesmen.external_salesman_id</v>
+      </c>
+      <c r="M1" t="str">
         <v>salesmen.phone_number</v>
       </c>
-      <c r="I1" t="str">
+      <c r="N1" t="str">
         <v>salesmen.zone</v>
       </c>
-      <c r="J1" t="str">
+      <c r="O1" t="str">
         <v>salesmen.region</v>
       </c>
-      <c r="K1" t="str">
+      <c r="P1" t="str">
         <v>salesmen.area</v>
       </c>
-      <c r="L1" t="str">
+      <c r="Q1" t="str">
         <v>outlets.external_outlet_code</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>outlets.outlet_name</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>outlets.mobile_number</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>outlets.gst_number</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>outlets.address_line1</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>outlets.address_line2</v>
       </c>
-      <c r="R1" t="str">
+      <c r="W1" t="str">
         <v>outlets.pincode</v>
       </c>
-      <c r="S1" t="str">
+      <c r="X1" t="str">
         <v>outlets.latitude</v>
       </c>
-      <c r="T1" t="str">
+      <c r="Y1" t="str">
         <v>outlets.longitude</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Z1" t="str">
         <v>outlets.zone</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AA1" t="str">
         <v>outlets.region</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AB1" t="str">
         <v>outlets.area</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AC1" t="str">
+        <v>tenant_outlets.tenant_outlet_code</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>brands.brand_code</v>
+      </c>
+      <c r="AE1" t="str">
         <v>brands.brand_name</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AF1" t="str">
         <v>skus.sku_code</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AG1" t="str">
         <v>skus.name</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AH1" t="str">
         <v>skus.hsn_code</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AI1" t="str">
         <v>skus.mrp</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AJ1" t="str">
         <v>skus.discount_amount</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AK1" t="str">
         <v>skus.discount_percent</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AL1" t="str">
         <v>skus.weight</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AM1" t="str">
         <v>skus.length_cm</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AN1" t="str">
         <v>skus.width_cm</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AO1" t="str">
         <v>skus.height_cm</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AP1" t="str">
         <v>skus.rate</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AQ1" t="str">
         <v>skus.sgst_percent</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AR1" t="str">
         <v>skus.sgst_amount</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AS1" t="str">
         <v>skus.cgst_percent</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AT1" t="str">
         <v>skus.cgst_amount</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AU1" t="str">
         <v>skus.amount</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AV1" t="str">
         <v>skus.igst_percent</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AW1" t="str">
         <v>skus.igst_amount</v>
       </c>
-      <c r="AQ1" t="str">
+      <c r="AX1" t="str">
         <v>sales_orders.external_order_id</v>
       </c>
-      <c r="AR1" t="str">
+      <c r="AY1" t="str">
         <v>sales_orders.external_invoice_no</v>
       </c>
-      <c r="AS1" t="str">
+      <c r="AZ1" t="str">
         <v>sales_orders.external_awb_no</v>
       </c>
-      <c r="AT1" t="str">
+      <c r="BA1" t="str">
         <v>sales_orders.order_punched_at</v>
       </c>
-      <c r="AU1" t="str">
+      <c r="BB1" t="str">
         <v>sales_orders.order_sale_date</v>
       </c>
-      <c r="AV1" t="str">
+      <c r="BC1" t="str">
         <v>sales_orders.gross_amount</v>
       </c>
-      <c r="AW1" t="str">
+      <c r="BD1" t="str">
         <v>sales_orders.discount_amount</v>
       </c>
-      <c r="AX1" t="str">
+      <c r="BE1" t="str">
         <v>sales_orders.tax_amount</v>
       </c>
-      <c r="AY1" t="str">
+      <c r="BF1" t="str">
         <v>sales_orders.net_amount</v>
       </c>
-      <c r="AZ1" t="str">
+      <c r="BG1" t="str">
         <v>sales_orders.collections_amount</v>
       </c>
-      <c r="BA1" t="str">
+      <c r="BH1" t="str">
         <v>sales_orders.outstanding_amount</v>
       </c>
-      <c r="BB1" t="str">
+      <c r="BI1" t="str">
         <v>sales_orders.decided_margin_amount</v>
       </c>
-      <c r="BC1" t="str">
+      <c r="BJ1" t="str">
         <v>sales_orders.remarks</v>
       </c>
-      <c r="BD1" t="str">
+      <c r="BK1" t="str">
+        <v>sales_order_items.external_line_id</v>
+      </c>
+      <c r="BL1" t="str">
         <v>sales_order_items.ordered_quantity</v>
       </c>
-      <c r="BE1" t="str">
+      <c r="BM1" t="str">
         <v>sales_order_items.rate</v>
       </c>
-      <c r="BF1" t="str">
+      <c r="BN1" t="str">
         <v>sales_order_items.discount_amount</v>
       </c>
-      <c r="BG1" t="str">
+      <c r="BO1" t="str">
         <v>sales_order_items.discount_percent</v>
       </c>
-      <c r="BH1" t="str">
+      <c r="BP1" t="str">
         <v>sales_order_items.sgst_percent</v>
       </c>
-      <c r="BI1" t="str">
+      <c r="BQ1" t="str">
         <v>sales_order_items.sgst_amount</v>
       </c>
-      <c r="BJ1" t="str">
+      <c r="BR1" t="str">
         <v>sales_order_items.cgst_percent</v>
       </c>
-      <c r="BK1" t="str">
+      <c r="BS1" t="str">
         <v>sales_order_items.cgst_amount</v>
       </c>
-      <c r="BL1" t="str">
+      <c r="BT1" t="str">
         <v>sales_order_items.igst_percent</v>
       </c>
-      <c r="BM1" t="str">
+      <c r="BU1" t="str">
         <v>sales_order_items.igst_amount</v>
       </c>
-      <c r="BN1" t="str">
+      <c r="BV1" t="str">
         <v>sales_order_items.tax_amount</v>
       </c>
-      <c r="BO1" t="str">
+      <c r="BW1" t="str">
         <v>sales_order_items.amount</v>
       </c>
-      <c r="BP1" t="str">
+      <c r="BX1" t="str">
         <v>order_payments.payment_date</v>
       </c>
-      <c r="BQ1" t="str">
+      <c r="BY1" t="str">
         <v>order_payments.payment_mode</v>
       </c>
-      <c r="BR1" t="str">
+      <c r="BZ1" t="str">
         <v>order_payments.amount</v>
       </c>
-      <c r="BS1" t="str">
+      <c r="CA1" t="str">
         <v>order_payments.external_ref</v>
       </c>
     </row>
@@ -619,213 +643,237 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
         <v>South Distribution LLP</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>BEAT_BLR_01</v>
+      </c>
+      <c r="H2" t="str">
         <v>Indiranagar Morning Beat</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
         <v>Ravi Kumar</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
+        <v>EMP_1001</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>9876543210</v>
       </c>
-      <c r="I2" t="str">
+      <c r="N2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="J2" t="str">
+      <c r="O2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="K2" t="str">
+      <c r="P2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="L2" t="str">
+      <c r="Q2" t="str">
         <v>OUT_0001</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>Annapurna Stores</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>9988776655</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>29ABCDE1234F1Z5</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>12, 100 Feet Rd</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>Indiranagar</v>
       </c>
-      <c r="R2" t="str">
+      <c r="W2" t="str">
         <v>560038</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>12.9715987</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>77.6400001</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Z2" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="V2" t="str">
+      <c r="AA2" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AB2" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="X2" t="str">
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v>BRAND_COLA</v>
+      </c>
+      <c r="AE2" t="str">
         <v>Super Cola</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="AF2" t="str">
         <v>SKU_COLA_250</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AG2" t="str">
         <v>Super Cola 250ml</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AH2" t="str">
         <v>22021020</v>
       </c>
-      <c r="AB2">
+      <c r="AI2">
         <v>20</v>
       </c>
-      <c r="AC2">
+      <c r="AJ2">
         <v>1</v>
       </c>
-      <c r="AD2">
+      <c r="AK2">
         <v>5</v>
       </c>
-      <c r="AE2">
+      <c r="AL2">
         <v>0.25</v>
       </c>
-      <c r="AF2">
+      <c r="AM2">
         <v>5</v>
       </c>
-      <c r="AG2">
+      <c r="AN2">
         <v>5</v>
       </c>
-      <c r="AH2">
+      <c r="AO2">
         <v>18</v>
       </c>
-      <c r="AI2">
+      <c r="AP2">
         <v>19</v>
       </c>
-      <c r="AJ2">
+      <c r="AQ2">
         <v>9</v>
       </c>
-      <c r="AK2">
+      <c r="AR2">
         <v>1.71</v>
       </c>
-      <c r="AL2">
+      <c r="AS2">
         <v>9</v>
       </c>
-      <c r="AM2">
+      <c r="AT2">
         <v>1.71</v>
       </c>
-      <c r="AN2">
+      <c r="AU2">
         <v>22.42</v>
       </c>
-      <c r="AO2">
+      <c r="AV2">
         <v>0</v>
       </c>
-      <c r="AP2">
+      <c r="AW2">
         <v>0</v>
       </c>
-      <c r="AQ2" t="str">
+      <c r="AX2" t="str">
         <v>ORD_10001</v>
       </c>
-      <c r="AR2" t="str">
+      <c r="AY2" t="str">
         <v>INV_10001</v>
       </c>
-      <c r="AS2" t="str">
+      <c r="AZ2" t="str">
         <v>AWB_50001</v>
       </c>
-      <c r="AT2" t="str">
+      <c r="BA2" t="str">
         <v>2026-03-10 10:30:00</v>
       </c>
-      <c r="AU2" t="str">
+      <c r="BB2" t="str">
         <v>2026-03-10</v>
       </c>
-      <c r="AV2">
+      <c r="BC2">
         <v>2000</v>
-      </c>
-      <c r="AW2">
-        <v>100</v>
-      </c>
-      <c r="AX2">
-        <v>342</v>
-      </c>
-      <c r="AY2">
-        <v>2242</v>
-      </c>
-      <c r="AZ2">
-        <v>1500</v>
-      </c>
-      <c r="BA2">
-        <v>742</v>
-      </c>
-      <c r="BB2">
-        <v>120</v>
-      </c>
-      <c r="BC2" t="str">
-        <v>Sample order with payment</v>
       </c>
       <c r="BD2">
         <v>100</v>
       </c>
       <c r="BE2">
+        <v>342</v>
+      </c>
+      <c r="BF2">
+        <v>2242</v>
+      </c>
+      <c r="BG2">
+        <v>1500</v>
+      </c>
+      <c r="BH2">
+        <v>742</v>
+      </c>
+      <c r="BI2">
+        <v>120</v>
+      </c>
+      <c r="BJ2" t="str">
+        <v>Sample order with payment</v>
+      </c>
+      <c r="BK2" t="str">
+        <v/>
+      </c>
+      <c r="BL2">
+        <v>100</v>
+      </c>
+      <c r="BM2">
         <v>19</v>
       </c>
-      <c r="BF2">
+      <c r="BN2">
         <v>100</v>
       </c>
-      <c r="BG2">
+      <c r="BO2">
         <v>5</v>
       </c>
-      <c r="BH2">
+      <c r="BP2">
         <v>9</v>
       </c>
-      <c r="BI2">
+      <c r="BQ2">
         <v>171</v>
       </c>
-      <c r="BJ2">
+      <c r="BR2">
         <v>9</v>
       </c>
-      <c r="BK2">
+      <c r="BS2">
         <v>171</v>
       </c>
-      <c r="BL2">
+      <c r="BT2">
         <v>0</v>
       </c>
-      <c r="BM2">
+      <c r="BU2">
         <v>0</v>
       </c>
-      <c r="BN2">
+      <c r="BV2">
         <v>342</v>
       </c>
-      <c r="BO2">
+      <c r="BW2">
         <v>2242</v>
       </c>
-      <c r="BP2" t="str">
+      <c r="BX2" t="str">
         <v>2026-03-11</v>
       </c>
-      <c r="BQ2" t="str">
+      <c r="BY2" t="str">
         <v>UPI</v>
       </c>
-      <c r="BR2">
+      <c r="BZ2">
         <v>1500</v>
       </c>
-      <c r="BS2" t="str">
+      <c r="CA2" t="str">
         <v>UPI123456789</v>
       </c>
     </row>
@@ -834,213 +882,237 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
         <v>South Distribution LLP</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v>BEAT_BLR_01</v>
+      </c>
+      <c r="H3" t="str">
         <v>Indiranagar Morning Beat</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>Ravi Kumar</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
+        <v>EMP_1001</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>9876543210</v>
       </c>
-      <c r="I3" t="str">
+      <c r="N3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="J3" t="str">
+      <c r="O3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="K3" t="str">
+      <c r="P3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="L3" t="str">
+      <c r="Q3" t="str">
         <v>OUT_0001</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>Annapurna Stores</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>9988776655</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>29ABCDE1234F1Z5</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>12, 100 Feet Rd</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>Indiranagar</v>
       </c>
-      <c r="R3" t="str">
+      <c r="W3" t="str">
         <v>560038</v>
       </c>
-      <c r="S3">
+      <c r="X3">
         <v>12.9715987</v>
       </c>
-      <c r="T3">
+      <c r="Y3">
         <v>77.6400001</v>
       </c>
-      <c r="U3" t="str">
+      <c r="Z3" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="V3" t="str">
+      <c r="AA3" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="W3" t="str">
+      <c r="AB3" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="X3" t="str">
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v>BRAND_COLA</v>
+      </c>
+      <c r="AE3" t="str">
         <v>Super Cola</v>
       </c>
-      <c r="Y3" t="str">
+      <c r="AF3" t="str">
         <v>SKU_COLA_500</v>
       </c>
-      <c r="Z3" t="str">
+      <c r="AG3" t="str">
         <v>Super Cola 500ml</v>
       </c>
-      <c r="AA3" t="str">
+      <c r="AH3" t="str">
         <v>22021020</v>
       </c>
-      <c r="AB3">
+      <c r="AI3">
         <v>35</v>
       </c>
-      <c r="AC3">
+      <c r="AJ3">
         <v>2</v>
       </c>
-      <c r="AD3">
+      <c r="AK3">
         <v>5.71</v>
       </c>
-      <c r="AE3">
+      <c r="AL3">
         <v>0.5</v>
       </c>
-      <c r="AF3">
+      <c r="AM3">
         <v>6</v>
       </c>
-      <c r="AG3">
+      <c r="AN3">
         <v>6</v>
       </c>
-      <c r="AH3">
+      <c r="AO3">
         <v>22</v>
       </c>
-      <c r="AI3">
+      <c r="AP3">
         <v>33</v>
       </c>
-      <c r="AJ3">
+      <c r="AQ3">
         <v>9</v>
       </c>
-      <c r="AK3">
+      <c r="AR3">
         <v>2.97</v>
       </c>
-      <c r="AL3">
+      <c r="AS3">
         <v>9</v>
       </c>
-      <c r="AM3">
+      <c r="AT3">
         <v>2.97</v>
       </c>
-      <c r="AN3">
+      <c r="AU3">
         <v>38.94</v>
       </c>
-      <c r="AO3">
+      <c r="AV3">
         <v>0</v>
       </c>
-      <c r="AP3">
+      <c r="AW3">
         <v>0</v>
       </c>
-      <c r="AQ3" t="str">
+      <c r="AX3" t="str">
         <v>ORD_10001</v>
       </c>
-      <c r="AR3" t="str">
+      <c r="AY3" t="str">
         <v>INV_10001</v>
       </c>
-      <c r="AS3" t="str">
+      <c r="AZ3" t="str">
         <v>AWB_50001</v>
       </c>
-      <c r="AT3" t="str">
+      <c r="BA3" t="str">
         <v>2026-03-10 10:30:00</v>
       </c>
-      <c r="AU3" t="str">
+      <c r="BB3" t="str">
         <v>2026-03-10</v>
       </c>
-      <c r="AV3">
+      <c r="BC3">
         <v>2000</v>
       </c>
-      <c r="AW3">
+      <c r="BD3">
         <v>100</v>
       </c>
-      <c r="AX3">
+      <c r="BE3">
         <v>342</v>
       </c>
-      <c r="AY3">
+      <c r="BF3">
         <v>2242</v>
       </c>
-      <c r="AZ3">
+      <c r="BG3">
         <v>1500</v>
       </c>
-      <c r="BA3">
+      <c r="BH3">
         <v>742</v>
       </c>
-      <c r="BB3">
+      <c r="BI3">
         <v>120</v>
       </c>
-      <c r="BC3" t="str">
+      <c r="BJ3" t="str">
         <v>Second line of same order</v>
       </c>
-      <c r="BD3">
+      <c r="BK3" t="str">
+        <v/>
+      </c>
+      <c r="BL3">
         <v>50</v>
       </c>
-      <c r="BE3">
+      <c r="BM3">
         <v>33</v>
       </c>
-      <c r="BF3">
+      <c r="BN3">
         <v>50</v>
       </c>
-      <c r="BG3">
+      <c r="BO3">
         <v>3.03</v>
       </c>
-      <c r="BH3">
+      <c r="BP3">
         <v>9</v>
       </c>
-      <c r="BI3">
+      <c r="BQ3">
         <v>148.5</v>
       </c>
-      <c r="BJ3">
+      <c r="BR3">
         <v>9</v>
       </c>
-      <c r="BK3">
+      <c r="BS3">
         <v>148.5</v>
       </c>
-      <c r="BL3">
+      <c r="BT3">
         <v>0</v>
       </c>
-      <c r="BM3">
+      <c r="BU3">
         <v>0</v>
       </c>
-      <c r="BN3">
+      <c r="BV3">
         <v>297</v>
       </c>
-      <c r="BO3">
+      <c r="BW3">
         <v>1947</v>
       </c>
-      <c r="BP3" t="str">
-        <v/>
-      </c>
-      <c r="BQ3" t="str">
-        <v/>
-      </c>
-      <c r="BR3" t="str">
-        <v/>
-      </c>
-      <c r="BS3" t="str">
+      <c r="BX3" t="str">
+        <v/>
+      </c>
+      <c r="BY3" t="str">
+        <v/>
+      </c>
+      <c r="BZ3" t="str">
+        <v/>
+      </c>
+      <c r="CA3" t="str">
         <v/>
       </c>
     </row>
@@ -1049,219 +1121,243 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
         <v>South Distribution LLP</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>BEAT_BLR_02</v>
+      </c>
+      <c r="H4" t="str">
         <v>Domlur Evening Beat</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v>Meera Nair</v>
       </c>
-      <c r="H4" t="str">
+      <c r="K4" t="str">
+        <v>EMP_1002</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>9123456780</v>
       </c>
-      <c r="I4" t="str">
+      <c r="N4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="J4" t="str">
+      <c r="O4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="K4" t="str">
+      <c r="P4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="L4" t="str">
+      <c r="Q4" t="str">
         <v>OUT_0002</v>
       </c>
-      <c r="M4" t="str">
+      <c r="R4" t="str">
         <v>Sri Ganesh Traders</v>
       </c>
-      <c r="N4" t="str">
+      <c r="S4" t="str">
         <v>9012345678</v>
       </c>
-      <c r="O4" t="str">
+      <c r="T4" t="str">
         <v>29ABCDE5678G1Z1</v>
       </c>
-      <c r="P4" t="str">
+      <c r="U4" t="str">
         <v>21, CMH Rd</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="V4" t="str">
         <v>Indiranagar</v>
       </c>
-      <c r="R4" t="str">
+      <c r="W4" t="str">
         <v>560038</v>
       </c>
-      <c r="S4">
+      <c r="X4">
         <v>12.975</v>
       </c>
-      <c r="T4">
+      <c r="Y4">
         <v>77.642</v>
       </c>
-      <c r="U4" t="str">
+      <c r="Z4" t="str">
         <v>SOUTH</v>
       </c>
-      <c r="V4" t="str">
+      <c r="AA4" t="str">
         <v>KARNATAKA</v>
       </c>
-      <c r="W4" t="str">
+      <c r="AB4" t="str">
         <v>BENGALURU</v>
       </c>
-      <c r="X4" t="str">
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v>BRAND_SNACKS</v>
+      </c>
+      <c r="AE4" t="str">
         <v>Crispy Bites</v>
       </c>
-      <c r="Y4" t="str">
+      <c r="AF4" t="str">
         <v>SKU_SNACK_100</v>
       </c>
-      <c r="Z4" t="str">
+      <c r="AG4" t="str">
         <v>Crispy Bites 100g</v>
       </c>
-      <c r="AA4" t="str">
+      <c r="AH4" t="str">
         <v>19059040</v>
       </c>
-      <c r="AB4">
+      <c r="AI4">
         <v>25</v>
       </c>
-      <c r="AC4">
+      <c r="AJ4">
         <v>1</v>
       </c>
-      <c r="AD4">
+      <c r="AK4">
         <v>4</v>
       </c>
-      <c r="AE4">
+      <c r="AL4">
         <v>0.1</v>
       </c>
-      <c r="AF4">
+      <c r="AM4">
         <v>12</v>
       </c>
-      <c r="AG4">
+      <c r="AN4">
         <v>8</v>
       </c>
-      <c r="AH4">
+      <c r="AO4">
         <v>4</v>
       </c>
-      <c r="AI4">
+      <c r="AP4">
         <v>22</v>
       </c>
-      <c r="AJ4">
+      <c r="AQ4">
         <v>6</v>
       </c>
-      <c r="AK4">
+      <c r="AR4">
         <v>1.32</v>
       </c>
-      <c r="AL4">
+      <c r="AS4">
         <v>6</v>
       </c>
-      <c r="AM4">
+      <c r="AT4">
         <v>1.32</v>
       </c>
-      <c r="AN4">
+      <c r="AU4">
         <v>24.64</v>
       </c>
-      <c r="AO4">
+      <c r="AV4">
         <v>0</v>
       </c>
-      <c r="AP4">
+      <c r="AW4">
         <v>0</v>
       </c>
-      <c r="AQ4" t="str">
+      <c r="AX4" t="str">
         <v>ORD_10002</v>
       </c>
-      <c r="AR4" t="str">
+      <c r="AY4" t="str">
         <v>INV_10002</v>
       </c>
-      <c r="AS4" t="str">
+      <c r="AZ4" t="str">
         <v>AWB_50002</v>
       </c>
-      <c r="AT4" t="str">
+      <c r="BA4" t="str">
         <v>2026-03-12 16:10:00</v>
       </c>
-      <c r="AU4" t="str">
+      <c r="BB4" t="str">
         <v>2026-03-12</v>
       </c>
-      <c r="AV4">
+      <c r="BC4">
         <v>1760</v>
-      </c>
-      <c r="AW4">
-        <v>80</v>
-      </c>
-      <c r="AX4">
-        <v>201.6</v>
-      </c>
-      <c r="AY4">
-        <v>1881.6</v>
-      </c>
-      <c r="AZ4">
-        <v>1000</v>
-      </c>
-      <c r="BA4">
-        <v>881.6</v>
-      </c>
-      <c r="BB4">
-        <v>95</v>
-      </c>
-      <c r="BC4" t="str">
-        <v>Second sample order</v>
       </c>
       <c r="BD4">
         <v>80</v>
       </c>
       <c r="BE4">
+        <v>201.6</v>
+      </c>
+      <c r="BF4">
+        <v>1881.6</v>
+      </c>
+      <c r="BG4">
+        <v>1000</v>
+      </c>
+      <c r="BH4">
+        <v>881.6</v>
+      </c>
+      <c r="BI4">
+        <v>95</v>
+      </c>
+      <c r="BJ4" t="str">
+        <v>Second sample order</v>
+      </c>
+      <c r="BK4" t="str">
+        <v/>
+      </c>
+      <c r="BL4">
+        <v>80</v>
+      </c>
+      <c r="BM4">
         <v>22</v>
       </c>
-      <c r="BF4">
+      <c r="BN4">
         <v>80</v>
       </c>
-      <c r="BG4">
+      <c r="BO4">
         <v>4.55</v>
       </c>
-      <c r="BH4">
+      <c r="BP4">
         <v>6</v>
       </c>
-      <c r="BI4">
+      <c r="BQ4">
         <v>100.8</v>
       </c>
-      <c r="BJ4">
+      <c r="BR4">
         <v>6</v>
       </c>
-      <c r="BK4">
+      <c r="BS4">
         <v>100.8</v>
       </c>
-      <c r="BL4">
+      <c r="BT4">
         <v>0</v>
       </c>
-      <c r="BM4">
+      <c r="BU4">
         <v>0</v>
       </c>
-      <c r="BN4">
+      <c r="BV4">
         <v>201.6</v>
       </c>
-      <c r="BO4">
+      <c r="BW4">
         <v>1881.6</v>
       </c>
-      <c r="BP4" t="str">
+      <c r="BX4" t="str">
         <v>2026-03-13</v>
       </c>
-      <c r="BQ4" t="str">
+      <c r="BY4" t="str">
         <v>CASH</v>
       </c>
-      <c r="BR4">
+      <c r="BZ4">
         <v>1000</v>
       </c>
-      <c r="BS4" t="str">
+      <c r="CA4" t="str">
         <v>CASH001</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BS4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CA4"/>
   </ignoredErrors>
 </worksheet>
 </file>